--- a/panchang-data/Nellore2026.xlsx
+++ b/panchang-data/Nellore2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5391">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16198,6 +16198,9 @@
   </si>
   <si>
     <t>121°05'08.29</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16687,7 +16690,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16773,7 +16776,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16859,7 +16862,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16945,7 +16948,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17031,7 +17034,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17117,7 +17120,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17203,7 +17206,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17289,7 +17292,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17375,7 +17378,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17461,7 +17464,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17547,7 +17550,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17633,7 +17636,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17719,7 +17722,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17805,7 +17808,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17891,7 +17894,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17977,7 +17980,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18063,7 +18066,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18149,7 +18152,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18235,7 +18238,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18321,7 +18324,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18407,7 +18410,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18493,7 +18496,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18579,7 +18582,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18665,7 +18668,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18751,7 +18754,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18837,7 +18840,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18923,7 +18926,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19009,7 +19012,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19095,7 +19098,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19181,7 +19184,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19267,7 +19270,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19353,7 +19356,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19439,7 +19442,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19525,7 +19528,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19611,7 +19614,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19697,7 +19700,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19783,7 +19786,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19869,7 +19872,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19955,7 +19958,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20041,7 +20044,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20127,7 +20130,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20213,7 +20216,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20299,7 +20302,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20385,7 +20388,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20471,7 +20474,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20557,7 +20560,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20643,7 +20646,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20729,7 +20732,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20815,7 +20818,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20901,7 +20904,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -20987,7 +20990,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21073,7 +21076,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21159,7 +21162,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21245,7 +21248,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21331,7 +21334,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21417,7 +21420,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21503,7 +21506,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21589,7 +21592,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21675,7 +21678,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21761,7 +21764,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21847,7 +21850,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21933,7 +21936,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22019,7 +22022,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22105,7 +22108,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22191,7 +22194,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22277,7 +22280,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22363,7 +22366,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22449,7 +22452,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22535,7 +22538,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22621,7 +22624,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22707,7 +22710,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22793,7 +22796,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22879,7 +22882,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22965,7 +22968,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23051,7 +23054,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23137,7 +23140,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23223,7 +23226,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23309,7 +23312,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23395,7 +23398,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23481,7 +23484,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23567,7 +23570,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23653,7 +23656,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23739,7 +23742,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23825,7 +23828,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23911,7 +23914,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -23997,7 +24000,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24083,7 +24086,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24169,7 +24172,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24255,7 +24258,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24341,7 +24344,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24427,7 +24430,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24513,7 +24516,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24599,7 +24602,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24685,7 +24688,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24771,7 +24774,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24857,7 +24860,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24943,7 +24946,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25029,7 +25032,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25115,7 +25118,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25201,7 +25204,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25287,7 +25290,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25373,7 +25376,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25459,7 +25462,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25545,7 +25548,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25631,7 +25634,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25717,7 +25720,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25803,7 +25806,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25889,7 +25892,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25975,7 +25978,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26061,7 +26064,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26147,7 +26150,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26233,7 +26236,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26319,7 +26322,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26405,7 +26408,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26491,7 +26494,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26577,7 +26580,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26663,7 +26666,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26749,7 +26752,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26835,7 +26838,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26921,7 +26924,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27007,7 +27010,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1451</v>
+        <v>1875</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27093,7 +27096,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27179,7 +27182,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27265,7 +27268,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27351,7 +27354,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27437,7 +27440,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27523,7 +27526,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27609,7 +27612,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27695,7 +27698,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27781,7 +27784,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27867,7 +27870,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27953,7 +27956,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28039,7 +28042,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28125,7 +28128,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28211,7 +28214,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28297,7 +28300,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28383,7 +28386,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28469,7 +28472,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28555,7 +28558,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28641,7 +28644,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28727,7 +28730,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28813,7 +28816,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28899,7 +28902,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -28985,7 +28988,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29071,7 +29074,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29157,7 +29160,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29243,7 +29246,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29329,7 +29332,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29415,7 +29418,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29501,7 +29504,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29587,7 +29590,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1875</v>
+        <v>5390</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29673,7 +29676,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29759,7 +29762,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29845,7 +29848,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29931,7 +29934,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30017,7 +30020,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30103,7 +30106,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30189,7 +30192,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30275,7 +30278,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30361,7 +30364,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30447,7 +30450,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30533,7 +30536,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30619,7 +30622,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30705,7 +30708,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30791,7 +30794,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30877,7 +30880,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2312</v>
+        <v>5390</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
